--- a/Hoadon/HD2026/HDVao/1/3502550210_HDDienTuKhongMa.xlsx
+++ b/Hoadon/HD2026/HDVao/1/3502550210_HDDienTuKhongMa.xlsx
@@ -255,17 +255,17 @@
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
+          <t>Địa chỉ người bán</t>
+        </is>
+      </c>
+      <c r="I6" s="3" t="inlineStr">
+        <is>
           <t>MST người mua/MST người nhận hàng</t>
         </is>
       </c>
-      <c r="I6" s="3" t="inlineStr">
+      <c r="J6" s="3" t="inlineStr">
         <is>
           <t>Tên người mua/Tên người nhận hàng</t>
-        </is>
-      </c>
-      <c r="J6" s="3" t="inlineStr">
-        <is>
-          <t>Địa chỉ người mua</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
@@ -325,50 +325,50 @@
       </c>
       <c r="C7" s="6" t="inlineStr">
         <is>
-          <t>K26TBB</t>
+          <t>K26THE</t>
         </is>
       </c>
       <c r="D7" s="7" t="inlineStr">
         <is>
-          <t>310</t>
+          <t>70591</t>
         </is>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>02/01/2026</t>
+          <t>01/01/2026</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>0100111948-043</t>
+          <t>0300954529</t>
         </is>
       </c>
       <c r="G7" s="6" t="inlineStr">
         <is>
-          <t>NGÂN HÀNG THƯƠNG MẠI CỔ PHẦN CÔNG THƯƠNG VIỆT NAM - CHI NHÁNH BÀ RỊA - VŨNG TÀU</t>
-        </is>
-      </c>
-      <c r="H7" s="7" t="inlineStr">
+          <t>CHI NHÁNH TẬP ĐOÀN BƯU CHÍNH VIỄN THÔNG VIỆT NAM (LOẠI HÌNH DOANH NGHIỆP: CÔNG TY TNHH) - VIỄN THÔNG THÀNH PHỐ HỒ CHÍ MINH</t>
+        </is>
+      </c>
+      <c r="H7" s="6"/>
+      <c r="I7" s="7" t="inlineStr">
         <is>
           <t>3502550210</t>
         </is>
       </c>
-      <c r="I7" s="6" t="inlineStr">
-        <is>
-          <t>CONG TY TNHH THANH HUONG BEN DINH</t>
-        </is>
-      </c>
-      <c r="J7" s="6"/>
+      <c r="J7" s="6" t="inlineStr">
+        <is>
+          <t>Công Ty TNHH Thạnh Hương Bến Đình</t>
+        </is>
+      </c>
       <c r="K7" s="13" t="n">
-        <v>35000.0</v>
+        <v>163453.0</v>
       </c>
       <c r="L7" s="13" t="n">
-        <v>3500.0</v>
+        <v>16345.0</v>
       </c>
       <c r="M7" s="13"/>
       <c r="N7" s="13"/>
       <c r="O7" s="13" t="n">
-        <v>38500.0</v>
+        <v>179798.0</v>
       </c>
       <c r="P7" s="7" t="inlineStr">
         <is>
@@ -407,7 +407,7 @@
       </c>
       <c r="D8" s="7" t="inlineStr">
         <is>
-          <t>70591</t>
+          <t>70593</t>
         </is>
       </c>
       <c r="E8" s="7" t="inlineStr">
@@ -425,27 +425,27 @@
           <t>CHI NHÁNH TẬP ĐOÀN BƯU CHÍNH VIỄN THÔNG VIỆT NAM (LOẠI HÌNH DOANH NGHIỆP: CÔNG TY TNHH) - VIỄN THÔNG THÀNH PHỐ HỒ CHÍ MINH</t>
         </is>
       </c>
-      <c r="H8" s="7" t="inlineStr">
+      <c r="H8" s="6"/>
+      <c r="I8" s="7" t="inlineStr">
         <is>
           <t>3502550210</t>
         </is>
       </c>
-      <c r="I8" s="6" t="inlineStr">
+      <c r="J8" s="6" t="inlineStr">
         <is>
           <t>Công Ty TNHH Thạnh Hương Bến Đình</t>
         </is>
       </c>
-      <c r="J8" s="6"/>
       <c r="K8" s="13" t="n">
-        <v>163453.0</v>
+        <v>192018.0</v>
       </c>
       <c r="L8" s="13" t="n">
-        <v>16345.0</v>
+        <v>19202.0</v>
       </c>
       <c r="M8" s="13"/>
       <c r="N8" s="13"/>
       <c r="O8" s="13" t="n">
-        <v>179798.0</v>
+        <v>211220.0</v>
       </c>
       <c r="P8" s="7" t="inlineStr">
         <is>
@@ -484,7 +484,7 @@
       </c>
       <c r="D9" s="7" t="inlineStr">
         <is>
-          <t>70593</t>
+          <t>70594</t>
         </is>
       </c>
       <c r="E9" s="7" t="inlineStr">
@@ -502,27 +502,27 @@
           <t>CHI NHÁNH TẬP ĐOÀN BƯU CHÍNH VIỄN THÔNG VIỆT NAM (LOẠI HÌNH DOANH NGHIỆP: CÔNG TY TNHH) - VIỄN THÔNG THÀNH PHỐ HỒ CHÍ MINH</t>
         </is>
       </c>
-      <c r="H9" s="7" t="inlineStr">
+      <c r="H9" s="6"/>
+      <c r="I9" s="7" t="inlineStr">
         <is>
           <t>3502550210</t>
         </is>
       </c>
-      <c r="I9" s="6" t="inlineStr">
+      <c r="J9" s="6" t="inlineStr">
         <is>
           <t>Công Ty TNHH Thạnh Hương Bến Đình</t>
         </is>
       </c>
-      <c r="J9" s="6"/>
       <c r="K9" s="13" t="n">
-        <v>192018.0</v>
+        <v>163636.0</v>
       </c>
       <c r="L9" s="13" t="n">
-        <v>19202.0</v>
+        <v>16364.0</v>
       </c>
       <c r="M9" s="13"/>
       <c r="N9" s="13"/>
       <c r="O9" s="13" t="n">
-        <v>211220.0</v>
+        <v>180000.0</v>
       </c>
       <c r="P9" s="7" t="inlineStr">
         <is>
@@ -540,237 +540,6 @@
         </is>
       </c>
       <c r="S9" s="6" t="inlineStr">
-        <is>
-          <t>Tổng cục thuế đã nhận không mã</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="4" t="n">
-        <v>4.0</v>
-      </c>
-      <c r="B10" s="7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C10" s="6" t="inlineStr">
-        <is>
-          <t>K26THE</t>
-        </is>
-      </c>
-      <c r="D10" s="7" t="inlineStr">
-        <is>
-          <t>70594</t>
-        </is>
-      </c>
-      <c r="E10" s="7" t="inlineStr">
-        <is>
-          <t>01/01/2026</t>
-        </is>
-      </c>
-      <c r="F10" s="7" t="inlineStr">
-        <is>
-          <t>0300954529</t>
-        </is>
-      </c>
-      <c r="G10" s="6" t="inlineStr">
-        <is>
-          <t>CHI NHÁNH TẬP ĐOÀN BƯU CHÍNH VIỄN THÔNG VIỆT NAM (LOẠI HÌNH DOANH NGHIỆP: CÔNG TY TNHH) - VIỄN THÔNG THÀNH PHỐ HỒ CHÍ MINH</t>
-        </is>
-      </c>
-      <c r="H10" s="7" t="inlineStr">
-        <is>
-          <t>3502550210</t>
-        </is>
-      </c>
-      <c r="I10" s="6" t="inlineStr">
-        <is>
-          <t>Công Ty TNHH Thạnh Hương Bến Đình</t>
-        </is>
-      </c>
-      <c r="J10" s="6"/>
-      <c r="K10" s="13" t="n">
-        <v>163636.0</v>
-      </c>
-      <c r="L10" s="13" t="n">
-        <v>16364.0</v>
-      </c>
-      <c r="M10" s="13"/>
-      <c r="N10" s="13"/>
-      <c r="O10" s="13" t="n">
-        <v>180000.0</v>
-      </c>
-      <c r="P10" s="7" t="inlineStr">
-        <is>
-          <t>VND</t>
-        </is>
-      </c>
-      <c r="Q10" s="7" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="R10" s="6" t="inlineStr">
-        <is>
-          <t>Hóa đơn mới</t>
-        </is>
-      </c>
-      <c r="S10" s="6" t="inlineStr">
-        <is>
-          <t>Tổng cục thuế đã nhận không mã</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="n">
-        <v>5.0</v>
-      </c>
-      <c r="B11" s="7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C11" s="6" t="inlineStr">
-        <is>
-          <t>K26TKE</t>
-        </is>
-      </c>
-      <c r="D11" s="7" t="inlineStr">
-        <is>
-          <t>21189</t>
-        </is>
-      </c>
-      <c r="E11" s="7" t="inlineStr">
-        <is>
-          <t>14/01/2026</t>
-        </is>
-      </c>
-      <c r="F11" s="7" t="inlineStr">
-        <is>
-          <t>0300954529</t>
-        </is>
-      </c>
-      <c r="G11" s="6" t="inlineStr">
-        <is>
-          <t>CHI NHÁNH TẬP ĐOÀN BƯU CHÍNH VIỄN THÔNG VIỆT NAM (LOẠI HÌNH DOANH NGHIỆP: CÔNG TY TNHH) - VIỄN THÔNG THÀNH PHỐ HỒ CHÍ MINH</t>
-        </is>
-      </c>
-      <c r="H11" s="7" t="inlineStr">
-        <is>
-          <t>3502550210</t>
-        </is>
-      </c>
-      <c r="I11" s="6" t="inlineStr">
-        <is>
-          <t>Công Ty TNHH Thạnh Hương Bến Đình</t>
-        </is>
-      </c>
-      <c r="J11" s="6"/>
-      <c r="K11" s="13" t="n">
-        <v>8000.0</v>
-      </c>
-      <c r="L11" s="13" t="n">
-        <v>800.0</v>
-      </c>
-      <c r="M11" s="13"/>
-      <c r="N11" s="13"/>
-      <c r="O11" s="13" t="n">
-        <v>8800.0</v>
-      </c>
-      <c r="P11" s="7" t="inlineStr">
-        <is>
-          <t>VND</t>
-        </is>
-      </c>
-      <c r="Q11" s="7" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="R11" s="6" t="inlineStr">
-        <is>
-          <t>Hóa đơn mới</t>
-        </is>
-      </c>
-      <c r="S11" s="6" t="inlineStr">
-        <is>
-          <t>Tổng cục thuế đã nhận không mã</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="4" t="n">
-        <v>6.0</v>
-      </c>
-      <c r="B12" s="7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="inlineStr">
-        <is>
-          <t>K26TKE</t>
-        </is>
-      </c>
-      <c r="D12" s="7" t="inlineStr">
-        <is>
-          <t>21193</t>
-        </is>
-      </c>
-      <c r="E12" s="7" t="inlineStr">
-        <is>
-          <t>14/01/2026</t>
-        </is>
-      </c>
-      <c r="F12" s="7" t="inlineStr">
-        <is>
-          <t>0300954529</t>
-        </is>
-      </c>
-      <c r="G12" s="6" t="inlineStr">
-        <is>
-          <t>CHI NHÁNH TẬP ĐOÀN BƯU CHÍNH VIỄN THÔNG VIỆT NAM (LOẠI HÌNH DOANH NGHIỆP: CÔNG TY TNHH) - VIỄN THÔNG THÀNH PHỐ HỒ CHÍ MINH</t>
-        </is>
-      </c>
-      <c r="H12" s="7" t="inlineStr">
-        <is>
-          <t>3502550210</t>
-        </is>
-      </c>
-      <c r="I12" s="6" t="inlineStr">
-        <is>
-          <t>Công Ty TNHH Thạnh Hương Bến Đình</t>
-        </is>
-      </c>
-      <c r="J12" s="6"/>
-      <c r="K12" s="13" t="n">
-        <v>8000.0</v>
-      </c>
-      <c r="L12" s="13" t="n">
-        <v>800.0</v>
-      </c>
-      <c r="M12" s="13"/>
-      <c r="N12" s="13"/>
-      <c r="O12" s="13" t="n">
-        <v>8800.0</v>
-      </c>
-      <c r="P12" s="7" t="inlineStr">
-        <is>
-          <t>VND</t>
-        </is>
-      </c>
-      <c r="Q12" s="7" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="R12" s="6" t="inlineStr">
-        <is>
-          <t>Hóa đơn mới</t>
-        </is>
-      </c>
-      <c r="S12" s="6" t="inlineStr">
         <is>
           <t>Tổng cục thuế đã nhận không mã</t>
         </is>
